--- a/Unity/Assets/Config/Excel/UnionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="UnionProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,12 +81,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="57">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>Id</t>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>XiuLianLevel</t>
+  </si>
+  <si>
+    <t>PeopleNum</t>
+  </si>
+  <si>
+    <t>DonateGold</t>
+  </si>
+  <si>
+    <t>DonateDiamond</t>
+  </si>
+  <si>
+    <t>DonateExp</t>
+  </si>
+  <si>
+    <t>DonateReward</t>
+  </si>
+  <si>
+    <t>UpAllReward</t>
+  </si>
+  <si>
+    <t>AddUnionGold</t>
+  </si>
+  <si>
+    <t>UnionGoldLimit</t>
+  </si>
+  <si>
+    <t>UnionGoldCost</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
   </si>
   <si>
     <t>升级经验</t>
@@ -120,48 +171,6 @@
   </si>
   <si>
     <t>消耗家族资金</t>
-  </si>
-  <si>
-    <t>Exp</t>
-  </si>
-  <si>
-    <t>XiuLianLevel</t>
-  </si>
-  <si>
-    <t>PeopleNum</t>
-  </si>
-  <si>
-    <t>DonateGold</t>
-  </si>
-  <si>
-    <t>DonateDiamond</t>
-  </si>
-  <si>
-    <t>DonateExp</t>
-  </si>
-  <si>
-    <t>DonateReward</t>
-  </si>
-  <si>
-    <t>UpAllReward</t>
-  </si>
-  <si>
-    <t>AddUnionGold</t>
-  </si>
-  <si>
-    <t>UnionGoldLimit</t>
-  </si>
-  <si>
-    <t>UnionGoldCost</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
   </si>
   <si>
     <t>家族1级</t>
@@ -255,7 +264,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -263,15 +272,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -686,21 +689,6 @@
       <top style="thin">
         <color indexed="9"/>
       </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
       <bottom style="hair">
         <color indexed="12"/>
       </bottom>
@@ -717,6 +705,21 @@
         <color indexed="9"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -850,175 +853,176 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2221,568 +2225,1005 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:HW61"/>
+  <dimension ref="A1:HV59"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="19.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="2" customWidth="1"/>
-    <col min="8" max="9" width="18.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="18.125" style="2" customWidth="1"/>
-    <col min="14" max="15" width="18.625" style="2" customWidth="1"/>
-    <col min="16" max="231" width="8.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="19.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="18.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="18.625" style="1" customWidth="1"/>
+    <col min="15" max="230" width="8.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="4:4">
-      <c r="D2" s="3" t="s">
+    <row r="1" customFormat="1" ht="20.1" customHeight="1" spans="1:230">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
+      <c r="CY1" s="1"/>
+      <c r="CZ1" s="1"/>
+      <c r="DA1" s="1"/>
+      <c r="DB1" s="1"/>
+      <c r="DC1" s="1"/>
+      <c r="DD1" s="1"/>
+      <c r="DE1" s="1"/>
+      <c r="DF1" s="1"/>
+      <c r="DG1" s="1"/>
+      <c r="DH1" s="1"/>
+      <c r="DI1" s="1"/>
+      <c r="DJ1" s="1"/>
+      <c r="DK1" s="1"/>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
+      <c r="DP1" s="1"/>
+      <c r="DQ1" s="1"/>
+      <c r="DR1" s="1"/>
+      <c r="DS1" s="1"/>
+      <c r="DT1" s="1"/>
+      <c r="DU1" s="1"/>
+      <c r="DV1" s="1"/>
+      <c r="DW1" s="1"/>
+      <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
+      <c r="DZ1" s="1"/>
+      <c r="EA1" s="1"/>
+      <c r="EB1" s="1"/>
+      <c r="EC1" s="1"/>
+      <c r="ED1" s="1"/>
+      <c r="EE1" s="1"/>
+      <c r="EF1" s="1"/>
+      <c r="EG1" s="1"/>
+      <c r="EH1" s="1"/>
+      <c r="EI1" s="1"/>
+      <c r="EJ1" s="1"/>
+      <c r="EK1" s="1"/>
+      <c r="EL1" s="1"/>
+      <c r="EM1" s="1"/>
+      <c r="EN1" s="1"/>
+      <c r="EO1" s="1"/>
+      <c r="EP1" s="1"/>
+      <c r="EQ1" s="1"/>
+      <c r="ER1" s="1"/>
+      <c r="ES1" s="1"/>
+      <c r="ET1" s="1"/>
+      <c r="EU1" s="1"/>
+      <c r="EV1" s="1"/>
+      <c r="EW1" s="1"/>
+      <c r="EX1" s="1"/>
+      <c r="EY1" s="1"/>
+      <c r="EZ1" s="1"/>
+      <c r="FA1" s="1"/>
+      <c r="FB1" s="1"/>
+      <c r="FC1" s="1"/>
+      <c r="FD1" s="1"/>
+      <c r="FE1" s="1"/>
+      <c r="FF1" s="1"/>
+      <c r="FG1" s="1"/>
+      <c r="FH1" s="1"/>
+      <c r="FI1" s="1"/>
+      <c r="FJ1" s="1"/>
+      <c r="FK1" s="1"/>
+      <c r="FL1" s="1"/>
+      <c r="FM1" s="1"/>
+      <c r="FN1" s="1"/>
+      <c r="FO1" s="1"/>
+      <c r="FP1" s="1"/>
+      <c r="FQ1" s="1"/>
+      <c r="FR1" s="1"/>
+      <c r="FS1" s="1"/>
+      <c r="FT1" s="1"/>
+      <c r="FU1" s="1"/>
+      <c r="FV1" s="1"/>
+      <c r="FW1" s="1"/>
+      <c r="FX1" s="1"/>
+      <c r="FY1" s="1"/>
+      <c r="FZ1" s="1"/>
+      <c r="GA1" s="1"/>
+      <c r="GB1" s="1"/>
+      <c r="GC1" s="1"/>
+      <c r="GD1" s="1"/>
+      <c r="GE1" s="1"/>
+      <c r="GF1" s="1"/>
+      <c r="GG1" s="1"/>
+      <c r="GH1" s="1"/>
+      <c r="GI1" s="1"/>
+      <c r="GJ1" s="1"/>
+      <c r="GK1" s="1"/>
+      <c r="GL1" s="1"/>
+      <c r="GM1" s="1"/>
+      <c r="GN1" s="1"/>
+      <c r="GO1" s="1"/>
+      <c r="GP1" s="1"/>
+      <c r="GQ1" s="1"/>
+      <c r="GR1" s="1"/>
+      <c r="GS1" s="1"/>
+      <c r="GT1" s="1"/>
+      <c r="GU1" s="1"/>
+      <c r="GV1" s="1"/>
+      <c r="GW1" s="1"/>
+      <c r="GX1" s="1"/>
+      <c r="GY1" s="1"/>
+      <c r="GZ1" s="1"/>
+      <c r="HA1" s="1"/>
+      <c r="HB1" s="1"/>
+      <c r="HC1" s="1"/>
+      <c r="HD1" s="1"/>
+      <c r="HE1" s="1"/>
+      <c r="HF1" s="1"/>
+      <c r="HG1" s="1"/>
+      <c r="HH1" s="1"/>
+      <c r="HI1" s="1"/>
+      <c r="HJ1" s="1"/>
+      <c r="HK1" s="1"/>
+      <c r="HL1" s="1"/>
+      <c r="HM1" s="1"/>
+      <c r="HN1" s="1"/>
+      <c r="HO1" s="1"/>
+      <c r="HP1" s="1"/>
+      <c r="HQ1" s="1"/>
+      <c r="HR1" s="1"/>
+      <c r="HS1" s="1"/>
+      <c r="HT1" s="1"/>
+      <c r="HU1" s="1"/>
+      <c r="HV1" s="1"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C3" s="4" t="s">
+    <row r="2" customFormat="1" ht="20.1" customHeight="1" spans="1:230">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
+      <c r="CN2" s="1"/>
+      <c r="CO2" s="1"/>
+      <c r="CP2" s="1"/>
+      <c r="CQ2" s="1"/>
+      <c r="CR2" s="1"/>
+      <c r="CS2" s="1"/>
+      <c r="CT2" s="1"/>
+      <c r="CU2" s="1"/>
+      <c r="CV2" s="1"/>
+      <c r="CW2" s="1"/>
+      <c r="CX2" s="1"/>
+      <c r="CY2" s="1"/>
+      <c r="CZ2" s="1"/>
+      <c r="DA2" s="1"/>
+      <c r="DB2" s="1"/>
+      <c r="DC2" s="1"/>
+      <c r="DD2" s="1"/>
+      <c r="DE2" s="1"/>
+      <c r="DF2" s="1"/>
+      <c r="DG2" s="1"/>
+      <c r="DH2" s="1"/>
+      <c r="DI2" s="1"/>
+      <c r="DJ2" s="1"/>
+      <c r="DK2" s="1"/>
+      <c r="DL2" s="1"/>
+      <c r="DM2" s="1"/>
+      <c r="DN2" s="1"/>
+      <c r="DO2" s="1"/>
+      <c r="DP2" s="1"/>
+      <c r="DQ2" s="1"/>
+      <c r="DR2" s="1"/>
+      <c r="DS2" s="1"/>
+      <c r="DT2" s="1"/>
+      <c r="DU2" s="1"/>
+      <c r="DV2" s="1"/>
+      <c r="DW2" s="1"/>
+      <c r="DX2" s="1"/>
+      <c r="DY2" s="1"/>
+      <c r="DZ2" s="1"/>
+      <c r="EA2" s="1"/>
+      <c r="EB2" s="1"/>
+      <c r="EC2" s="1"/>
+      <c r="ED2" s="1"/>
+      <c r="EE2" s="1"/>
+      <c r="EF2" s="1"/>
+      <c r="EG2" s="1"/>
+      <c r="EH2" s="1"/>
+      <c r="EI2" s="1"/>
+      <c r="EJ2" s="1"/>
+      <c r="EK2" s="1"/>
+      <c r="EL2" s="1"/>
+      <c r="EM2" s="1"/>
+      <c r="EN2" s="1"/>
+      <c r="EO2" s="1"/>
+      <c r="EP2" s="1"/>
+      <c r="EQ2" s="1"/>
+      <c r="ER2" s="1"/>
+      <c r="ES2" s="1"/>
+      <c r="ET2" s="1"/>
+      <c r="EU2" s="1"/>
+      <c r="EV2" s="1"/>
+      <c r="EW2" s="1"/>
+      <c r="EX2" s="1"/>
+      <c r="EY2" s="1"/>
+      <c r="EZ2" s="1"/>
+      <c r="FA2" s="1"/>
+      <c r="FB2" s="1"/>
+      <c r="FC2" s="1"/>
+      <c r="FD2" s="1"/>
+      <c r="FE2" s="1"/>
+      <c r="FF2" s="1"/>
+      <c r="FG2" s="1"/>
+      <c r="FH2" s="1"/>
+      <c r="FI2" s="1"/>
+      <c r="FJ2" s="1"/>
+      <c r="FK2" s="1"/>
+      <c r="FL2" s="1"/>
+      <c r="FM2" s="1"/>
+      <c r="FN2" s="1"/>
+      <c r="FO2" s="1"/>
+      <c r="FP2" s="1"/>
+      <c r="FQ2" s="1"/>
+      <c r="FR2" s="1"/>
+      <c r="FS2" s="1"/>
+      <c r="FT2" s="1"/>
+      <c r="FU2" s="1"/>
+      <c r="FV2" s="1"/>
+      <c r="FW2" s="1"/>
+      <c r="FX2" s="1"/>
+      <c r="FY2" s="1"/>
+      <c r="FZ2" s="1"/>
+      <c r="GA2" s="1"/>
+      <c r="GB2" s="1"/>
+      <c r="GC2" s="1"/>
+      <c r="GD2" s="1"/>
+      <c r="GE2" s="1"/>
+      <c r="GF2" s="1"/>
+      <c r="GG2" s="1"/>
+      <c r="GH2" s="1"/>
+      <c r="GI2" s="1"/>
+      <c r="GJ2" s="1"/>
+      <c r="GK2" s="1"/>
+      <c r="GL2" s="1"/>
+      <c r="GM2" s="1"/>
+      <c r="GN2" s="1"/>
+      <c r="GO2" s="1"/>
+      <c r="GP2" s="1"/>
+      <c r="GQ2" s="1"/>
+      <c r="GR2" s="1"/>
+      <c r="GS2" s="1"/>
+      <c r="GT2" s="1"/>
+      <c r="GU2" s="1"/>
+      <c r="GV2" s="1"/>
+      <c r="GW2" s="1"/>
+      <c r="GX2" s="1"/>
+      <c r="GY2" s="1"/>
+      <c r="GZ2" s="1"/>
+      <c r="HA2" s="1"/>
+      <c r="HB2" s="1"/>
+      <c r="HC2" s="1"/>
+      <c r="HD2" s="1"/>
+      <c r="HE2" s="1"/>
+      <c r="HF2" s="1"/>
+      <c r="HG2" s="1"/>
+      <c r="HH2" s="1"/>
+      <c r="HI2" s="1"/>
+      <c r="HJ2" s="1"/>
+      <c r="HK2" s="1"/>
+      <c r="HL2" s="1"/>
+      <c r="HM2" s="1"/>
+      <c r="HN2" s="1"/>
+      <c r="HO2" s="1"/>
+      <c r="HP2" s="1"/>
+      <c r="HQ2" s="1"/>
+      <c r="HR2" s="1"/>
+      <c r="HS2" s="1"/>
+      <c r="HT2" s="1"/>
+      <c r="HU2" s="1"/>
+      <c r="HV2" s="1"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="7">
+        <v>500</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7">
+        <v>200000</v>
+      </c>
+      <c r="H4" s="7">
+        <v>180</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="7">
+        <v>50000000</v>
+      </c>
+      <c r="N4" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="C5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>18</v>
+      </c>
+      <c r="G5" s="7">
+        <v>210000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>180</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="7">
+        <f>M4+50000000</f>
+        <v>100000000</v>
+      </c>
+      <c r="N5" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="2:230">
+      <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="C6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1800</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7">
+        <v>220000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>180</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" ref="M6:M13" si="0">M5+50000000</f>
+        <v>150000000</v>
+      </c>
+      <c r="N6" s="7">
+        <v>100</v>
+      </c>
+      <c r="HV6"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="2:230">
+      <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="7">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="8">
-        <v>500</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>15</v>
-      </c>
-      <c r="H6" s="8">
-        <v>200000</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="G7" s="7">
+        <v>230000</v>
+      </c>
+      <c r="H7" s="7">
         <v>180</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="8">
-        <v>50000000</v>
-      </c>
-      <c r="O6" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C7" s="8">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="I7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="8">
-        <v>2</v>
-      </c>
-      <c r="G7" s="8">
-        <v>18</v>
-      </c>
-      <c r="H7" s="8">
-        <v>210000</v>
-      </c>
-      <c r="I7" s="8">
-        <v>180</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="8">
-        <f>N6+50000000</f>
-        <v>100000000</v>
-      </c>
-      <c r="O7" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:231">
-      <c r="C8" s="8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="K7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="8">
-        <v>1800</v>
-      </c>
-      <c r="F8" s="8">
-        <v>3</v>
-      </c>
-      <c r="G8" s="8">
-        <v>21</v>
-      </c>
-      <c r="H8" s="8">
-        <v>220000</v>
-      </c>
-      <c r="I8" s="8">
-        <v>180</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="8">
-        <f t="shared" ref="N8:N15" si="0">N7+50000000</f>
-        <v>150000000</v>
-      </c>
-      <c r="O8" s="8">
-        <v>100</v>
-      </c>
-      <c r="HW8"/>
-    </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:231">
-      <c r="C9" s="8">
-        <v>4</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2800</v>
-      </c>
-      <c r="F9" s="8">
-        <v>4</v>
-      </c>
-      <c r="G9" s="8">
-        <v>24</v>
-      </c>
-      <c r="H9" s="8">
-        <v>230000</v>
-      </c>
-      <c r="I9" s="8">
-        <v>180</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="M7" s="7">
         <f t="shared" si="0"/>
         <v>200000000</v>
       </c>
-      <c r="O9" s="8">
+      <c r="N7" s="7">
         <v>100</v>
       </c>
-      <c r="HW9"/>
+      <c r="HV7"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C10" s="8">
+    <row r="8" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="C8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="7">
         <v>4000</v>
       </c>
-      <c r="F10" s="8">
+      <c r="E8" s="7">
         <v>5</v>
       </c>
-      <c r="G10" s="8">
+      <c r="F8" s="7">
         <v>27</v>
       </c>
-      <c r="H10" s="8">
+      <c r="G8" s="7">
         <v>240000</v>
       </c>
-      <c r="I10" s="8">
+      <c r="H8" s="7">
         <v>180</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="8">
+      <c r="I8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="7">
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="O10" s="8">
+      <c r="N8" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C11" s="8">
+    <row r="9" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="C9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="7">
         <v>5500</v>
       </c>
-      <c r="F11" s="8">
+      <c r="E9" s="7">
         <v>6</v>
       </c>
-      <c r="G11" s="8">
+      <c r="F9" s="7">
         <v>30</v>
       </c>
-      <c r="H11" s="8">
+      <c r="G9" s="7">
         <v>250000</v>
       </c>
-      <c r="I11" s="8">
+      <c r="H9" s="7">
         <v>180</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="8">
+      <c r="I9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="7">
         <f t="shared" si="0"/>
         <v>300000000</v>
       </c>
-      <c r="O11" s="8">
+      <c r="N9" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C12" s="8">
+    <row r="10" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="C10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="7">
         <v>7500</v>
       </c>
-      <c r="F12" s="8">
+      <c r="E10" s="7">
         <v>7</v>
       </c>
-      <c r="G12" s="8">
+      <c r="F10" s="7">
         <v>33</v>
       </c>
-      <c r="H12" s="8">
+      <c r="G10" s="7">
         <v>260000</v>
       </c>
-      <c r="I12" s="8">
+      <c r="H10" s="7">
         <v>180</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="8">
+      <c r="I10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" s="7">
         <f t="shared" si="0"/>
         <v>350000000</v>
       </c>
-      <c r="O12" s="8">
+      <c r="N10" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C13" s="8">
+    <row r="11" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="7">
         <v>10000</v>
       </c>
-      <c r="F13" s="8">
+      <c r="E11" s="7">
         <v>8</v>
       </c>
-      <c r="G13" s="8">
+      <c r="F11" s="7">
         <v>36</v>
       </c>
-      <c r="H13" s="8">
+      <c r="G11" s="7">
         <v>270000</v>
       </c>
-      <c r="I13" s="8">
+      <c r="H11" s="7">
         <v>180</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="8">
+      <c r="I11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="7">
         <f t="shared" si="0"/>
         <v>400000000</v>
       </c>
-      <c r="O13" s="8">
+      <c r="N11" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C14" s="8">
+    <row r="12" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="C12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="7">
         <v>13000</v>
       </c>
-      <c r="F14" s="8">
+      <c r="E12" s="7">
         <v>9</v>
       </c>
-      <c r="G14" s="8">
+      <c r="F12" s="7">
         <v>38</v>
       </c>
-      <c r="H14" s="8">
+      <c r="G12" s="7">
         <v>285000</v>
       </c>
-      <c r="I14" s="8">
+      <c r="H12" s="7">
         <v>180</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="8">
+      <c r="I12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="7">
         <f t="shared" si="0"/>
         <v>450000000</v>
       </c>
-      <c r="O14" s="8">
+      <c r="N12" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:15">
-      <c r="C15" s="8">
+    <row r="13" ht="20.1" customHeight="1" spans="2:14">
+      <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="C13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="7">
         <v>16500</v>
       </c>
-      <c r="F15" s="8">
+      <c r="E13" s="7">
         <v>10</v>
       </c>
-      <c r="G15" s="8">
+      <c r="F13" s="7">
         <v>40</v>
       </c>
-      <c r="H15" s="8">
+      <c r="G13" s="7">
         <v>300000</v>
       </c>
-      <c r="I15" s="8">
+      <c r="H13" s="7">
         <v>180</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="8">
+      <c r="I13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="7">
         <f t="shared" si="0"/>
         <v>500000000</v>
       </c>
-      <c r="O15" s="8">
+      <c r="N13" s="7">
         <v>100</v>
       </c>
     </row>
+    <row r="14" ht="20.1" customHeight="1"/>
+    <row r="15" ht="20.1" customHeight="1"/>
     <row r="16" ht="20.1" customHeight="1"/>
     <row r="17" ht="20.1" customHeight="1"/>
     <row r="18" ht="20.1" customHeight="1"/>
@@ -2827,8 +3268,6 @@
     <row r="57" ht="20.1" customHeight="1"/>
     <row r="58" ht="20.1" customHeight="1"/>
     <row r="59" ht="20.1" customHeight="1"/>
-    <row r="60" ht="20.1" customHeight="1"/>
-    <row r="61" ht="20.1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
